--- a/data/timisoara/km_data.xlsx
+++ b/data/timisoara/km_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,15 +490,135 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2500</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-27 11:01:25</t>
+          <t>2026-04-09 13:21:52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:52</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:06</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:21:07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
